--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH14"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.15"/>
   <cols>
     <col width="16.2109375" customWidth="1" style="7" min="3" max="3"/>
@@ -943,7 +943,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" s="7">
       <c r="A12" s="9" t="n"/>
       <c r="B12" s="9" t="n">
         <v>20004</v>
@@ -1025,7 +1025,7 @@
       <c r="AG12" s="9" t="n"/>
       <c r="AH12" s="9" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" s="7">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="9" t="n"/>
@@ -1077,7 +1077,7 @@
       <c r="AG13" s="9" t="n"/>
       <c r="AH13" s="9" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" s="7">
       <c r="A14" s="9" t="n"/>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="9" t="n"/>
@@ -1149,6 +1149,774 @@
       <c r="AG14" s="9" t="n"/>
       <c r="AH14" s="9" t="n"/>
     </row>
+    <row r="15" s="7">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n">
+        <v>20010</v>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>持续喷火</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="E15" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>表现轨道</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>播放喷火动作</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>TaskPlayCue</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>CuePlayGameCoreAnimator</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>Attack</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n"/>
+      <c r="W15" s="9" t="n"/>
+      <c r="X15" s="9" t="n"/>
+      <c r="Y15" s="9" t="n"/>
+      <c r="Z15" s="9" t="n"/>
+      <c r="AA15" s="9" t="n"/>
+      <c r="AB15" s="9" t="n"/>
+      <c r="AC15" s="9" t="n"/>
+      <c r="AD15" s="9" t="n"/>
+      <c r="AE15" s="9" t="n"/>
+      <c r="AF15" s="9" t="n"/>
+      <c r="AG15" s="9" t="n"/>
+      <c r="AH15" s="9" t="n"/>
+    </row>
+    <row r="16" s="7">
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>播放喷火流</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>TaskPlayCue</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>CueMountPrefab</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>Assets/Prefabs/Abilities/World/喷火-火焰表现.prefab</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>0,0,0</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>0,0,0</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+      <c r="X16" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9" t="n"/>
+      <c r="AF16" s="9" t="n"/>
+      <c r="AG16" s="9" t="n"/>
+      <c r="AH16" s="9" t="n"/>
+    </row>
+    <row r="17" s="7">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>播放喷火音效</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>TaskPlayCue</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>CuePlayGameCoreAudio</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>3b7e4c26c0a18a74ea6711d1d29f0312</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="n"/>
+      <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="9" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="9" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="9" t="n"/>
+      <c r="Y17" s="9" t="n"/>
+      <c r="Z17" s="9" t="n"/>
+      <c r="AA17" s="9" t="n"/>
+      <c r="AB17" s="9" t="n"/>
+      <c r="AC17" s="9" t="n"/>
+      <c r="AD17" s="9" t="n"/>
+      <c r="AE17" s="9" t="n"/>
+      <c r="AF17" s="9" t="n"/>
+      <c r="AG17" s="9" t="n"/>
+      <c r="AH17" s="9" t="n"/>
+    </row>
+    <row r="18" s="7">
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>世界元素轨道</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>持续施加火元素</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyWorldElement</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="9" t="n"/>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="9" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="9" t="n"/>
+      <c r="Z18" s="9" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="9" t="n"/>
+      <c r="AC18" s="9" t="n"/>
+      <c r="AD18" s="9" t="n"/>
+      <c r="AE18" s="9" t="n"/>
+      <c r="AF18" s="9" t="n"/>
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="9" t="n"/>
+    </row>
+    <row r="19" s="7">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>角色命中轨道</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>喷火命中1</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyEffects</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>CatchAreaPolygon2D</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>0.2,-0.3;1.2,-0.7;3.2,-1.8;3.2,1.8;1.2,0.7;0.2,0.3</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="9" t="n"/>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="9" t="n"/>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="9" t="n"/>
+      <c r="W19" s="9" t="n"/>
+      <c r="X19" s="9" t="n"/>
+      <c r="Y19" s="9" t="n"/>
+      <c r="Z19" s="9" t="n"/>
+      <c r="AA19" s="9" t="n"/>
+      <c r="AB19" s="9" t="n"/>
+      <c r="AC19" s="9" t="n"/>
+      <c r="AD19" s="9" t="n"/>
+      <c r="AE19" s="9" t="n"/>
+      <c r="AF19" s="9" t="n"/>
+      <c r="AG19" s="9" t="n"/>
+      <c r="AH19" s="9" t="n"/>
+    </row>
+    <row r="20" s="7">
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>喷火命中2</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyEffects</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>CatchAreaPolygon2D</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>0.2,-0.3;1.2,-0.7;3.2,-1.8;3.2,1.8;1.2,0.7;0.2,0.3</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="9" t="n"/>
+      <c r="S20" s="9" t="n"/>
+      <c r="T20" s="9" t="n"/>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="9" t="n"/>
+      <c r="W20" s="9" t="n"/>
+      <c r="X20" s="9" t="n"/>
+      <c r="Y20" s="9" t="n"/>
+      <c r="Z20" s="9" t="n"/>
+      <c r="AA20" s="9" t="n"/>
+      <c r="AB20" s="9" t="n"/>
+      <c r="AC20" s="9" t="n"/>
+      <c r="AD20" s="9" t="n"/>
+      <c r="AE20" s="9" t="n"/>
+      <c r="AF20" s="9" t="n"/>
+      <c r="AG20" s="9" t="n"/>
+      <c r="AH20" s="9" t="n"/>
+    </row>
+    <row r="21" s="7">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>喷火命中3</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyEffects</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>CatchAreaPolygon2D</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>0.2,-0.3;1.2,-0.7;3.2,-1.8;3.2,1.8;1.2,0.7;0.2,0.3</t>
+        </is>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="9" t="n"/>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="9" t="n"/>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="9" t="n"/>
+      <c r="W21" s="9" t="n"/>
+      <c r="X21" s="9" t="n"/>
+      <c r="Y21" s="9" t="n"/>
+      <c r="Z21" s="9" t="n"/>
+      <c r="AA21" s="9" t="n"/>
+      <c r="AB21" s="9" t="n"/>
+      <c r="AC21" s="9" t="n"/>
+      <c r="AD21" s="9" t="n"/>
+      <c r="AE21" s="9" t="n"/>
+      <c r="AF21" s="9" t="n"/>
+      <c r="AG21" s="9" t="n"/>
+      <c r="AH21" s="9" t="n"/>
+    </row>
+    <row r="22" s="7">
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>喷火命中4</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyEffects</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>CatchAreaPolygon2D</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>0.2,-0.3;1.2,-0.7;3.2,-1.8;3.2,1.8;1.2,0.7;0.2,0.3</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="9" t="n"/>
+      <c r="S22" s="9" t="n"/>
+      <c r="T22" s="9" t="n"/>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="9" t="n"/>
+      <c r="W22" s="9" t="n"/>
+      <c r="X22" s="9" t="n"/>
+      <c r="Y22" s="9" t="n"/>
+      <c r="Z22" s="9" t="n"/>
+      <c r="AA22" s="9" t="n"/>
+      <c r="AB22" s="9" t="n"/>
+      <c r="AC22" s="9" t="n"/>
+      <c r="AD22" s="9" t="n"/>
+      <c r="AE22" s="9" t="n"/>
+      <c r="AF22" s="9" t="n"/>
+      <c r="AG22" s="9" t="n"/>
+      <c r="AH22" s="9" t="n"/>
+    </row>
+    <row r="23" s="7">
+      <c r="A23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>喷火命中5</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyEffects</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>CatchAreaPolygon2D</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9" t="inlineStr">
+        <is>
+          <t>0.2,-0.3;1.2,-0.7;3.2,-1.8;3.2,1.8;1.2,0.7;0.2,0.3</t>
+        </is>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="9" t="n"/>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="9" t="n"/>
+      <c r="W23" s="9" t="n"/>
+      <c r="X23" s="9" t="n"/>
+      <c r="Y23" s="9" t="n"/>
+      <c r="Z23" s="9" t="n"/>
+      <c r="AA23" s="9" t="n"/>
+      <c r="AB23" s="9" t="n"/>
+      <c r="AC23" s="9" t="n"/>
+      <c r="AD23" s="9" t="n"/>
+      <c r="AE23" s="9" t="n"/>
+      <c r="AF23" s="9" t="n"/>
+      <c r="AG23" s="9" t="n"/>
+      <c r="AH23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>喷火命中6</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyEffects</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>CatchAreaPolygon2D</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9" t="inlineStr">
+        <is>
+          <t>0.2,-0.3;1.2,-0.7;3.2,-1.8;3.2,1.8;1.2,0.7;0.2,0.3</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="9" t="n"/>
+      <c r="W24" s="9" t="n"/>
+      <c r="X24" s="9" t="n"/>
+      <c r="Y24" s="9" t="n"/>
+      <c r="Z24" s="9" t="n"/>
+      <c r="AA24" s="9" t="n"/>
+      <c r="AB24" s="9" t="n"/>
+      <c r="AC24" s="9" t="n"/>
+      <c r="AD24" s="9" t="n"/>
+      <c r="AE24" s="9" t="n"/>
+      <c r="AF24" s="9" t="n"/>
+      <c r="AG24" s="9" t="n"/>
+      <c r="AH24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>喷火命中7</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>TaskApplyEffects</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>CatchAreaPolygon2D</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
+          <t>0.2,-0.3;1.2,-0.7;3.2,-1.8;3.2,1.8;1.2,0.7;0.2,0.3</t>
+        </is>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="9" t="n"/>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="9" t="n"/>
+      <c r="U25" s="9" t="n"/>
+      <c r="V25" s="9" t="n"/>
+      <c r="W25" s="9" t="n"/>
+      <c r="X25" s="9" t="n"/>
+      <c r="Y25" s="9" t="n"/>
+      <c r="Z25" s="9" t="n"/>
+      <c r="AA25" s="9" t="n"/>
+      <c r="AB25" s="9" t="n"/>
+      <c r="AC25" s="9" t="n"/>
+      <c r="AD25" s="9" t="n"/>
+      <c r="AE25" s="9" t="n"/>
+      <c r="AF25" s="9" t="n"/>
+      <c r="AG25" s="9" t="n"/>
+      <c r="AH25" s="9" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="G3:J3"/>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -1271,7 +1271,7 @@
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>Assets/Prefabs/Abilities/World/喷火-火焰表现.prefab</t>
+          <t>addbfd0e48c6444897677b61945321ef</t>
         </is>
       </c>
       <c r="O16" s="9" t="inlineStr">
